--- a/output/pdf_financials_xlsx/OC.xlsx
+++ b/output/pdf_financials_xlsx/OC.xlsx
@@ -1234,7 +1234,7 @@
         <v>0.661365</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.74453</v>
+        <v>-0.74453</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-0.786783</v>
@@ -1287,7 +1287,7 @@
         <v>-0.159638</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.32273</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -1501,16 +1501,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.336448</v>
+        <v>-1.336448</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.52138</v>
+        <v>-0.52138</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.661365</v>
+        <v>-0.661365</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.74453</v>
+        <v>-0.74453</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-0.786783</v>
@@ -1669,16 +1669,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.336448</v>
+        <v>-1.336448</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.52138</v>
+        <v>-0.52138</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.661365</v>
+        <v>-0.661365</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.74453</v>
+        <v>-0.74453</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-0.786783</v>
@@ -1944,7 +1944,7 @@
         <v>0.717181</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.7793949999999999</v>
+        <v>-0.709665</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.786783</v>
@@ -2056,7 +2056,7 @@
         <v>0.7209370000000001</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.782122</v>
+        <v>-0.706938</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.786783</v>
@@ -2173,10 +2173,10 @@
         <v>44.13034704292009</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -25799,7 +25799,7 @@
         <v>-0.561875</v>
       </c>
       <c r="M204" s="5" t="n">
-        <v>1.227291</v>
+        <v>-1.227291</v>
       </c>
       <c r="N204" t="inlineStr">
         <is>
@@ -45365,10 +45365,10 @@
         </is>
       </c>
       <c r="G422" s="5" t="n">
-        <v>0.661365</v>
+        <v>-0.661365</v>
       </c>
       <c r="H422" s="5" t="n">
-        <v>0.74453</v>
+        <v>-0.74453</v>
       </c>
       <c r="I422" t="inlineStr">
         <is>
@@ -46543,10 +46543,10 @@
         </is>
       </c>
       <c r="F435" s="5" t="n">
-        <v>0.52138</v>
+        <v>-0.52138</v>
       </c>
       <c r="G435" s="5" t="n">
-        <v>0.661365</v>
+        <v>-0.661365</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
@@ -47359,10 +47359,10 @@
         </is>
       </c>
       <c r="E444" s="5" t="n">
-        <v>1.336448</v>
+        <v>-1.336448</v>
       </c>
       <c r="F444" s="5" t="n">
-        <v>0.52138</v>
+        <v>-0.52138</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/OC.xlsx
+++ b/output/pdf_financials_xlsx/OC.xlsx
@@ -1013,31 +1013,31 @@
         <v>-0.034865</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.021391</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.058195</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.019112</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.017713</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.027119</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.010509</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.002175</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.065347</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.104745</v>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
@@ -1947,31 +1947,31 @@
         <v>-0.709665</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.786783</v>
+        <v>-0.8081739999999999</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.397839</v>
+        <v>-1.456034</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>2.408268</v>
+        <v>2.389156</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.695875</v>
+        <v>-0.713588</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.719291</v>
+        <v>1.692172</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-5.518403</v>
+        <v>-5.528912</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.808015</v>
+        <v>-1.81019</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.753566</v>
+        <v>-3.818913</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.63062</v>
+        <v>0.525875</v>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
@@ -2059,31 +2059,31 @@
         <v>-0.706938</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.786783</v>
+        <v>-0.8081739999999999</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.397839</v>
+        <v>-1.456034</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.408268</v>
+        <v>2.389156</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.695875</v>
+        <v>-0.713588</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.798995</v>
+        <v>1.771876</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-5.438699</v>
+        <v>-5.449208</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.808015</v>
+        <v>-1.81019</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.753566</v>
+        <v>-3.818913</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.63062</v>
+        <v>0.525875</v>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
@@ -2123,31 +2123,31 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-74.06647675817545</v>
+        <v>-76.08019083732323</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>12522.07291946609</v>
+        <v>13043.3933530413</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>67.22512019200573</v>
+        <v>66.69162205263353</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-234.7819779211315</v>
+        <v>-240.7581851062107</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>65.89778379166425</v>
+        <v>64.9044058230506</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>107.3884117561574</v>
+        <v>107.5959144731022</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>579.1207559256887</v>
+        <v>579.8174247277386</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>88.44948088242917</v>
+        <v>89.9893254534915</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>44.51905624853072</v>
+        <v>37.12451033062082</v>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
@@ -2324,19 +2324,19 @@
         <v>0.614657</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.291293</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.30138</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.761919</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.150797</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.327829</v>
       </c>
     </row>
     <row r="35">
@@ -2428,19 +2428,19 @@
         <v>0.614657</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.291293</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.30138</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.761919</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.150797</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.327829</v>
       </c>
     </row>
     <row r="37">
@@ -7115,10 +7115,10 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.103961</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.105841</v>
       </c>
       <c r="L124" s="3" t="n">
         <v>0</v>
@@ -7167,10 +7167,10 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.103961</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.105841</v>
       </c>
       <c r="L125" s="3" t="n">
         <v>0</v>
@@ -7873,7 +7873,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -27632,7 +27632,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -36201,7 +36205,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -39300,7 +39304,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">

--- a/output/pdf_financials_xlsx/OC.xlsx
+++ b/output/pdf_financials_xlsx/OC.xlsx
@@ -1252,10 +1252,10 @@
         <v>1.719291</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-5.518403</v>
+        <v>-6.114403</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-1.808015</v>
+        <v>-2.101015</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-3.753566</v>
@@ -1308,10 +1308,10 @@
         <v>-0.492</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>0.596</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>0.293</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0</v>
@@ -1962,10 +1962,10 @@
         <v>1.692172</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-5.528912</v>
+        <v>-6.124912</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.81019</v>
+        <v>-2.10319</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-3.818913</v>
@@ -2074,10 +2074,10 @@
         <v>1.771876</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-5.449208</v>
+        <v>-6.045208</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.81019</v>
+        <v>-2.10319</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-3.818913</v>
@@ -2138,10 +2138,10 @@
         <v>64.9044058230506</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>107.5959144731022</v>
+        <v>119.3640769337697</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>579.8174247277386</v>
+        <v>673.6675208199872</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>89.9893254534915</v>
@@ -2194,10 +2194,10 @@
         <v>28.61644712849657</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0</v>
+        <v>-9.747476572937702</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0</v>
+        <v>-13.94564055944389</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0</v>
@@ -3486,16 +3486,16 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>0</v>
+        <v>0.027683</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>0.029283</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>0.029283</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>0.029283</v>
       </c>
       <c r="F56" s="3" t="n">
         <v>0</v>
@@ -3538,16 +3538,16 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>0</v>
+        <v>0.010148</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>0.015139</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>0.018895</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>0.021622</v>
       </c>
       <c r="F57" s="3" t="n">
         <v>0</v>
@@ -4088,22 +4088,22 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.057776</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.184617</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.027085</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.030959</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.030459</v>
       </c>
       <c r="L67" s="3" t="n">
         <v>0</v>
@@ -4112,10 +4112,10 @@
         <v>0</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.07623199999999999</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.03692</v>
       </c>
       <c r="P67" s="3" t="n">
         <v>0</v>
@@ -6600,7 +6600,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>0</v>
+        <v>-1.156324</v>
       </c>
       <c r="N114" s="3" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-0.099563</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-0.03023</v>
       </c>
       <c r="L121" s="3" t="n">
         <v>0</v>
@@ -6971,13 +6971,13 @@
         <v>0</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-0.07668</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-0.08729099999999999</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-0.065843</v>
       </c>
     </row>
     <row r="122">
@@ -23981,7 +23981,11 @@
           <t>Share repurchase</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -25124,7 +25128,11 @@
           <t>Gain on acquisition of investments</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -25668,7 +25676,11 @@
           <t>Shares issued for acquisition of investments $</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -25844,7 +25856,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -26837,7 +26853,11 @@
           <t>Deferred income tax (recovery)</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -27543,7 +27563,11 @@
           <t>Share repurchase (Note 11)</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -28081,7 +28105,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -38669,7 +38697,11 @@
           <t>Income tax recovery (Note 12)</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -40202,7 +40234,11 @@
           <t>Income tax (recovery) (Note 16)</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
